--- a/media/Levels/Level_12.ver2.0xlsx.xlsx
+++ b/media/Levels/Level_12.ver2.0xlsx.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuuta\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\ドキュメント\2024年３月特別授業\BaseCross64\DoctorRemote\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C251CB5C-62FC-451F-91E3-AA4F1DD3C1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154B67FD-3302-457D-A977-C586879D7533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -9350,7 +9350,7 @@
       <c r="U107" s="1">
         <v>0</v>
       </c>
-      <c r="AK107" s="1">
+      <c r="AL107" s="1">
         <v>0</v>
       </c>
       <c r="BD107" s="1">
@@ -9373,11 +9373,11 @@
       <c r="U108" s="1">
         <v>2</v>
       </c>
-      <c r="AK108" s="1">
+      <c r="AL108" s="1">
         <v>2</v>
       </c>
       <c r="BD108" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CL108" s="1">
         <v>0</v>
@@ -9396,11 +9396,14 @@
       <c r="U109" s="1">
         <v>0</v>
       </c>
-      <c r="AK109" s="1">
+      <c r="AL109" s="1">
         <v>0</v>
       </c>
       <c r="BD109" s="1">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="BJ109">
+        <v>7</v>
       </c>
       <c r="CL109" s="1">
         <v>2</v>
@@ -9419,10 +9422,10 @@
       <c r="U110" s="1">
         <v>0</v>
       </c>
-      <c r="AK110" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD110" s="1">
+      <c r="AL110" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD110" s="3">
         <v>0</v>
       </c>
       <c r="CL110" s="1">
@@ -9442,11 +9445,11 @@
       <c r="U111" s="1">
         <v>2</v>
       </c>
-      <c r="AK111" s="1">
+      <c r="AL111" s="1">
         <v>2</v>
       </c>
       <c r="BD111" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="CL111" s="3">
         <v>0</v>
@@ -9465,11 +9468,11 @@
       <c r="U112" s="1">
         <v>0</v>
       </c>
-      <c r="AK112" s="1">
+      <c r="AL112" s="1">
         <v>0</v>
       </c>
       <c r="BD112" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CL112" s="3">
         <v>8</v>
@@ -9488,10 +9491,10 @@
       <c r="U113" s="1">
         <v>0</v>
       </c>
-      <c r="AK113" s="1">
-        <v>0</v>
-      </c>
-      <c r="BD113" s="3">
+      <c r="AL113" s="1">
+        <v>0</v>
+      </c>
+      <c r="BD113" s="1">
         <v>0</v>
       </c>
       <c r="CL113" s="3">
@@ -9511,11 +9514,11 @@
       <c r="U114" s="1">
         <v>2</v>
       </c>
-      <c r="AK114" s="1">
+      <c r="AL114" s="1">
         <v>2</v>
       </c>
       <c r="BD114" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CL114" s="1">
         <v>0</v>
@@ -9534,11 +9537,11 @@
       <c r="U115" s="1">
         <v>0</v>
       </c>
-      <c r="AK115" s="1">
+      <c r="AL115" s="1">
         <v>0</v>
       </c>
       <c r="BD115" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CL115" s="1">
         <v>2</v>
@@ -9569,71 +9572,68 @@
       <c r="W116" s="4">
         <v>0</v>
       </c>
-      <c r="AK116" s="1">
-        <v>0</v>
-      </c>
       <c r="AL116" s="1">
         <v>0</v>
       </c>
       <c r="AM116" s="1">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="1">
         <v>1</v>
       </c>
-      <c r="AN116" s="1">
-        <v>0</v>
-      </c>
       <c r="AO116" s="1">
         <v>0</v>
       </c>
       <c r="AP116" s="1">
+        <v>0</v>
+      </c>
+      <c r="AQ116" s="1">
         <v>1</v>
       </c>
-      <c r="AQ116" s="1">
-        <v>0</v>
-      </c>
       <c r="AR116" s="1">
         <v>0</v>
       </c>
       <c r="AS116" s="1">
+        <v>0</v>
+      </c>
+      <c r="AT116" s="1">
         <v>1</v>
       </c>
-      <c r="AT116" s="1">
-        <v>0</v>
-      </c>
       <c r="AU116" s="1">
         <v>0</v>
       </c>
       <c r="AV116" s="1">
+        <v>0</v>
+      </c>
+      <c r="AW116" s="1">
         <v>1</v>
       </c>
-      <c r="AW116" s="1">
-        <v>0</v>
-      </c>
       <c r="AX116" s="1">
         <v>0</v>
       </c>
       <c r="AY116" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ116" s="1">
         <v>1</v>
       </c>
-      <c r="AZ116" s="1">
-        <v>0</v>
-      </c>
       <c r="BA116" s="1">
         <v>0</v>
       </c>
       <c r="BB116" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC116" s="1">
         <v>1</v>
       </c>
-      <c r="BC116" s="1">
-        <v>0</v>
-      </c>
       <c r="BD116" s="1">
         <v>0</v>
       </c>
       <c r="BE116" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF116" s="1">
         <v>1</v>
-      </c>
-      <c r="BF116" s="1">
-        <v>0</v>
       </c>
       <c r="BG116" s="1">
         <v>0</v>
@@ -9877,10 +9877,10 @@
       <c r="W117" s="4">
         <v>0</v>
       </c>
-      <c r="AK117" s="1">
-        <v>2</v>
-      </c>
-      <c r="BO117" s="1">
+      <c r="AL117" s="1">
+        <v>2</v>
+      </c>
+      <c r="BP117" s="1">
         <v>0</v>
       </c>
       <c r="BV117" s="1">
@@ -9930,10 +9930,10 @@
       <c r="W118" s="4">
         <v>0</v>
       </c>
-      <c r="AK118" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO118" s="1">
+      <c r="AL118" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP118" s="1">
         <v>2</v>
       </c>
       <c r="BV118" s="1">
@@ -9983,10 +9983,10 @@
       <c r="W119" s="4">
         <v>0</v>
       </c>
-      <c r="AK119" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO119" s="1">
+      <c r="AL119" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP119" s="1">
         <v>0</v>
       </c>
       <c r="BV119" s="1">
@@ -10036,10 +10036,10 @@
       <c r="W120" s="4">
         <v>0</v>
       </c>
-      <c r="AK120" s="1">
-        <v>2</v>
-      </c>
-      <c r="BO120" s="1">
+      <c r="AL120" s="1">
+        <v>2</v>
+      </c>
+      <c r="BP120" s="1">
         <v>0</v>
       </c>
       <c r="BV120" s="1">
@@ -10077,10 +10077,10 @@
       <c r="U121" s="1">
         <v>0</v>
       </c>
-      <c r="AK121" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO121" s="1">
+      <c r="AL121" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP121" s="1">
         <v>2</v>
       </c>
       <c r="BV121" s="1">
@@ -10106,7 +10106,7 @@
       <c r="U122" s="1">
         <v>2</v>
       </c>
-      <c r="BO122" s="1">
+      <c r="BP122" s="1">
         <v>0</v>
       </c>
       <c r="BV122" s="1">
@@ -10132,7 +10132,7 @@
       <c r="U123" s="1">
         <v>0</v>
       </c>
-      <c r="BO123" s="1">
+      <c r="BP123" s="1">
         <v>0</v>
       </c>
       <c r="BV123" s="1">
@@ -10158,7 +10158,7 @@
       <c r="U124" s="1">
         <v>0</v>
       </c>
-      <c r="BO124" s="1">
+      <c r="BP124" s="1">
         <v>2</v>
       </c>
       <c r="BV124" s="1">
@@ -10184,7 +10184,7 @@
       <c r="U125" s="1">
         <v>2</v>
       </c>
-      <c r="BO125" s="1">
+      <c r="BP125" s="1">
         <v>0</v>
       </c>
       <c r="BV125" s="1">
@@ -10225,7 +10225,7 @@
       <c r="U126" s="1">
         <v>0</v>
       </c>
-      <c r="BO126" s="1">
+      <c r="BP126" s="1">
         <v>0</v>
       </c>
       <c r="BV126" s="1">
@@ -10281,7 +10281,7 @@
       <c r="U127" s="1">
         <v>0</v>
       </c>
-      <c r="BO127" s="1">
+      <c r="BP127" s="1">
         <v>2</v>
       </c>
       <c r="BV127" s="1">
@@ -10337,7 +10337,7 @@
       <c r="U128" s="1">
         <v>2</v>
       </c>
-      <c r="BO128" s="1">
+      <c r="BP128" s="1">
         <v>0</v>
       </c>
       <c r="BV128" s="1">
@@ -10393,7 +10393,7 @@
       <c r="U129" s="1">
         <v>0</v>
       </c>
-      <c r="BO129" s="1">
+      <c r="BP129" s="1">
         <v>0</v>
       </c>
       <c r="BV129" s="1">
@@ -10449,7 +10449,7 @@
       <c r="U130" s="1">
         <v>0</v>
       </c>
-      <c r="BO130" s="1">
+      <c r="BP130" s="1">
         <v>2</v>
       </c>
       <c r="BV130" s="1">
@@ -10490,10 +10490,10 @@
       <c r="U131" s="1">
         <v>2</v>
       </c>
-      <c r="AK131" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO131" s="1">
+      <c r="AL131" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP131" s="1">
         <v>0</v>
       </c>
       <c r="BV131" s="1">
@@ -10519,10 +10519,10 @@
       <c r="U132" s="1">
         <v>0</v>
       </c>
-      <c r="AK132" s="1">
-        <v>2</v>
-      </c>
-      <c r="BO132" s="1">
+      <c r="AL132" s="1">
+        <v>2</v>
+      </c>
+      <c r="BP132" s="1">
         <v>0</v>
       </c>
       <c r="BV132" s="1">
@@ -10548,10 +10548,10 @@
       <c r="U133" s="1">
         <v>0</v>
       </c>
-      <c r="AK133" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO133" s="1">
+      <c r="AL133" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP133" s="1">
         <v>2</v>
       </c>
       <c r="BV133" s="1">
@@ -10589,10 +10589,10 @@
       <c r="U134" s="1">
         <v>2</v>
       </c>
-      <c r="AK134" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO134" s="1">
+      <c r="AL134" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP134" s="1">
         <v>0</v>
       </c>
       <c r="BV134" s="1">
@@ -10630,10 +10630,10 @@
       <c r="U135" s="1">
         <v>0</v>
       </c>
-      <c r="AK135" s="1">
-        <v>2</v>
-      </c>
-      <c r="BO135" s="1">
+      <c r="AL135" s="1">
+        <v>2</v>
+      </c>
+      <c r="BP135" s="1">
         <v>0</v>
       </c>
       <c r="BV135" s="1">
@@ -10698,10 +10698,10 @@
       <c r="W136" s="4">
         <v>0</v>
       </c>
-      <c r="AK136" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO136" s="1">
+      <c r="AL136" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP136" s="1">
         <v>2</v>
       </c>
       <c r="BV136" s="1">
@@ -10766,10 +10766,10 @@
       <c r="W137" s="4">
         <v>0</v>
       </c>
-      <c r="AK137" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO137" s="1">
+      <c r="AL137" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP137" s="1">
         <v>0</v>
       </c>
       <c r="BV137" s="1">
@@ -10834,10 +10834,10 @@
       <c r="W138" s="4">
         <v>0</v>
       </c>
-      <c r="AK138" s="1">
-        <v>2</v>
-      </c>
-      <c r="BO138" s="1">
+      <c r="AL138" s="1">
+        <v>2</v>
+      </c>
+      <c r="BP138" s="1">
         <v>0</v>
       </c>
       <c r="BV138" s="1">
@@ -10890,10 +10890,10 @@
       <c r="W139" s="4">
         <v>0</v>
       </c>
-      <c r="AK139" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO139" s="1">
+      <c r="AL139" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP139" s="1">
         <v>2</v>
       </c>
       <c r="BV139" s="1">
@@ -10946,97 +10946,97 @@
       <c r="W140" s="4">
         <v>0</v>
       </c>
-      <c r="AK140" s="1">
-        <v>0</v>
-      </c>
       <c r="AL140" s="1">
+        <v>0</v>
+      </c>
+      <c r="AM140" s="1">
         <v>1</v>
       </c>
-      <c r="AM140" s="1">
-        <v>0</v>
-      </c>
       <c r="AN140" s="1">
         <v>0</v>
       </c>
       <c r="AO140" s="1">
+        <v>0</v>
+      </c>
+      <c r="AP140" s="1">
         <v>1</v>
       </c>
-      <c r="AP140" s="1">
-        <v>0</v>
-      </c>
       <c r="AQ140" s="1">
         <v>0</v>
       </c>
       <c r="AR140" s="1">
+        <v>0</v>
+      </c>
+      <c r="AS140" s="1">
         <v>1</v>
       </c>
-      <c r="AS140" s="1">
-        <v>0</v>
-      </c>
       <c r="AT140" s="1">
         <v>0</v>
       </c>
       <c r="AU140" s="1">
+        <v>0</v>
+      </c>
+      <c r="AV140" s="1">
         <v>1</v>
       </c>
-      <c r="AV140" s="1">
-        <v>0</v>
-      </c>
       <c r="AW140" s="1">
         <v>0</v>
       </c>
       <c r="AX140" s="1">
+        <v>0</v>
+      </c>
+      <c r="AY140" s="1">
         <v>1</v>
       </c>
-      <c r="AY140" s="1">
-        <v>0</v>
-      </c>
       <c r="AZ140" s="1">
         <v>0</v>
       </c>
       <c r="BA140" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB140" s="1">
         <v>1</v>
       </c>
-      <c r="BB140" s="1">
-        <v>0</v>
-      </c>
       <c r="BC140" s="1">
         <v>0</v>
       </c>
       <c r="BD140" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE140" s="1">
         <v>1</v>
       </c>
-      <c r="BE140" s="1">
-        <v>0</v>
-      </c>
       <c r="BF140" s="1">
         <v>0</v>
       </c>
       <c r="BG140" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH140" s="1">
         <v>1</v>
       </c>
-      <c r="BH140" s="1">
-        <v>0</v>
-      </c>
       <c r="BI140" s="1">
         <v>0</v>
       </c>
       <c r="BJ140" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK140" s="1">
         <v>1</v>
       </c>
-      <c r="BK140" s="1">
-        <v>0</v>
-      </c>
       <c r="BL140" s="1">
         <v>0</v>
       </c>
       <c r="BM140" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN140" s="1">
         <v>1</v>
       </c>
-      <c r="BN140" s="1">
-        <v>0</v>
-      </c>
       <c r="BO140" s="1">
+        <v>0</v>
+      </c>
+      <c r="BP140" s="1">
         <v>0</v>
       </c>
       <c r="BV140" s="1">

--- a/media/Levels/Level_12.ver2.0xlsx.xlsx
+++ b/media/Levels/Level_12.ver2.0xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154B67FD-3302-457D-A977-C586879D7533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D700E1-C1A3-4C42-AC85-85CD93625658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="1296" yWindow="2484" windowWidth="17280" windowHeight="9480" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/media/Levels/Level_12.ver2.0xlsx.xlsx
+++ b/media/Levels/Level_12.ver2.0xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D700E1-C1A3-4C42-AC85-85CD93625658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4F11C7-ED5D-41AF-8B82-824E362EC19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1296" yWindow="2484" windowWidth="17280" windowHeight="9480" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -9402,9 +9402,6 @@
       <c r="BD109" s="1">
         <v>0</v>
       </c>
-      <c r="BJ109">
-        <v>7</v>
-      </c>
       <c r="CL109" s="1">
         <v>2</v>
       </c>
